--- a/rzr_datos.xlsx
+++ b/rzr_datos.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,15 @@
           <t>kjsbdvshjbs</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ujfhgvnb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rzr_datos.xlsx
+++ b/rzr_datos.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="RZR" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +11,7 @@
     <sheet name="Operaciones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -52,7 +51,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,7 +415,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -473,7 +472,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -505,8 +504,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -558,15 +557,6 @@
           <t>kjsbdvshjbs</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ujfhgvnb</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -579,8 +569,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -642,6 +632,66 @@
       </c>
       <c r="D3" t="n">
         <v>1400000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Malacuata</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Can Am turbo s</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Venta</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Maverck xrs4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Renta</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Maverck xrs4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Renta</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>70000</v>
       </c>
     </row>
   </sheetData>

--- a/rzr_datos.xlsx
+++ b/rzr_datos.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">

--- a/rzr_datos.xlsx
+++ b/rzr_datos.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="RZR" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +12,7 @@
     <sheet name="Operaciones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -51,7 +52,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,8 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -438,15 +439,20 @@
           <t>Cantidad</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maverick R</t>
+          <t>turbo s</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>800000</v>
+        <v>50000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -454,17 +460,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Can Am turbo s</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>750000</v>
+        <v>400000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -472,25 +481,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Maverck xrs4</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Deportivo</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -504,8 +498,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -527,34 +521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>654531</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ljsjdhcjkabds</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Malacuata</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8465415</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>kjsbdvshjbs</t>
+          <t>hola</t>
         </is>
       </c>
     </row>
@@ -569,8 +536,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -592,106 +559,6 @@
         <is>
           <t>Precio</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Maverick R</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Malacuata</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Maverck xrs4</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Malacuata</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Can Am turbo s</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Venta</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Maverck xrs4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Renta</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andrey</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Maverck xrs4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Renta</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>70000</v>
       </c>
     </row>
   </sheetData>
